--- a/Lab_4/data/partB/param_optimization_process/v150_k10_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k10_s200_results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -573,34 +573,34 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,46 +674,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -726,34 +726,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -762,13 +762,13 @@
         <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>9</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,37 +842,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -894,13 +894,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>55</v>
@@ -909,22 +909,22 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,31 +998,31 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,28 +1059,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1099,34 +1099,34 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1145,28 +1145,28 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
         <v>55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>7</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1270,22 +1270,22 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
       </c>
       <c r="P16" t="n">
         <v>63</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
